--- a/en/downloads/data-excel/9.2.2.xlsx
+++ b/en/downloads/data-excel/9.2.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24075" windowHeight="12135"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -486,7 +486,7 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -577,6 +577,18 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -899,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.140625" customWidth="1"/>
@@ -909,7 +921,7 @@
     <col min="11" max="11" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="38.25">
+    <row r="1" spans="1:18" ht="38.25">
       <c r="A1" s="21" t="s">
         <v>43</v>
       </c>
@@ -928,7 +940,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
@@ -947,7 +959,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1">
+    <row r="3" spans="1:18" ht="15.75" thickBot="1">
       <c r="A3" s="11"/>
       <c r="B3" s="2"/>
       <c r="C3" s="10"/>
@@ -960,7 +972,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -1012,8 +1024,11 @@
       <c r="Q4" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="37">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="16" t="s">
         <v>38</v>
       </c>
@@ -1065,8 +1080,11 @@
       <c r="Q5" s="25">
         <v>10.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="38">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="12" t="s">
         <v>15</v>
       </c>
@@ -1118,8 +1136,11 @@
       <c r="Q6" s="24">
         <v>10.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="39">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="12" t="s">
         <v>16</v>
       </c>
@@ -1171,8 +1192,11 @@
       <c r="Q7" s="24">
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="39">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="12" t="s">
         <v>17</v>
       </c>
@@ -1224,8 +1248,11 @@
       <c r="Q8" s="24">
         <v>11.4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="39">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="12" t="s">
         <v>18</v>
       </c>
@@ -1277,8 +1304,11 @@
       <c r="Q9" s="24">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="39">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="12" t="s">
         <v>48</v>
       </c>
@@ -1330,8 +1360,11 @@
       <c r="Q10" s="24">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="39">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="12" t="s">
         <v>19</v>
       </c>
@@ -1383,8 +1416,11 @@
       <c r="Q11" s="24">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="39">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="12" t="s">
         <v>20</v>
       </c>
@@ -1436,8 +1472,11 @@
       <c r="Q12" s="24">
         <v>17.100000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="39">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="13" t="s">
         <v>21</v>
       </c>
@@ -1489,8 +1528,11 @@
       <c r="Q13" s="24">
         <v>17.7</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" s="23" customFormat="1">
+      <c r="R13" s="39">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="23" customFormat="1">
       <c r="A14" s="13" t="s">
         <v>22</v>
       </c>
@@ -1542,8 +1584,11 @@
       <c r="Q14" s="27">
         <v>9.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="39">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="26" t="s">
         <v>44</v>
       </c>
@@ -1565,7 +1610,7 @@
       <c r="M15" s="28"/>
       <c r="N15" s="28"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16" s="17" t="s">
         <v>32</v>
       </c>
@@ -1617,8 +1662,11 @@
       <c r="Q16" s="27">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="15.75" thickBot="1">
+      <c r="R16" s="39">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15.75" thickBot="1">
       <c r="A17" s="18" t="s">
         <v>33</v>
       </c>
@@ -1670,8 +1718,11 @@
       <c r="Q17" s="31">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" ht="22.5">
+      <c r="R17" s="40">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="22.5">
       <c r="A18" s="34" t="s">
         <v>37</v>
       </c>
@@ -1682,7 +1733,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:18">
       <c r="B21" s="19"/>
     </row>
   </sheetData>
